--- a/erp-server/erp-server-file/src/main/resources/excel/wms/packingTaskExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/packingTaskExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>装箱任务</t>
   </si>
@@ -37,6 +37,9 @@
     <t>关联单号</t>
   </si>
   <si>
+    <t>业务单号</t>
+  </si>
+  <si>
     <t>单据类型</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.businessCode}</t>
   </si>
   <si>
     <t>{.sourceTypeName}</t>
@@ -1105,33 +1111,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
-    <col min="2" max="2" width="19.125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="19.875" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="24.75" customWidth="1"/>
-    <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="16.875" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="36.375" customWidth="1"/>
-    <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="8.875" customWidth="1"/>
-    <col min="19" max="19" width="31.25" customWidth="1"/>
-    <col min="21" max="21" width="17.375" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="2" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="14.875" customWidth="1"/>
+    <col min="13" max="13" width="16.875" customWidth="1"/>
+    <col min="14" max="14" width="14.875" customWidth="1"/>
+    <col min="15" max="15" width="9" customWidth="1"/>
+    <col min="16" max="16" width="36.375" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="19" max="19" width="8.875" customWidth="1"/>
+    <col min="20" max="20" width="31.25" customWidth="1"/>
+    <col min="22" max="22" width="17.375" customWidth="1"/>
+    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1162,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -1171,46 +1177,52 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:13">
+    <row r="2" s="1" customFormat="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/packingTaskExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/packingTaskExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>装箱任务</t>
   </si>
@@ -52,9 +52,6 @@
     <t>发货数量</t>
   </si>
   <si>
-    <t>拣货数量</t>
-  </si>
-  <si>
     <t>已装箱数</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>{.deliveryQty}</t>
-  </si>
-  <si>
-    <t>{.pickedQty}</t>
   </si>
   <si>
     <t>{.packedQty}</t>
@@ -757,10 +751,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1111,7 +1105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1120,24 +1114,23 @@
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="19.875" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
-    <col min="8" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="24.75" customWidth="1"/>
-    <col min="12" max="12" width="14.875" customWidth="1"/>
-    <col min="13" max="13" width="16.875" customWidth="1"/>
-    <col min="14" max="14" width="14.875" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="36.375" customWidth="1"/>
-    <col min="17" max="17" width="10.375" customWidth="1"/>
-    <col min="19" max="19" width="8.875" customWidth="1"/>
-    <col min="20" max="20" width="31.25" customWidth="1"/>
-    <col min="22" max="22" width="17.375" customWidth="1"/>
-    <col min="24" max="24" width="9.375" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
+    <col min="10" max="10" width="24.75" customWidth="1"/>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="16.875" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="36.375" customWidth="1"/>
+    <col min="16" max="16" width="10.375" customWidth="1"/>
+    <col min="18" max="18" width="8.875" customWidth="1"/>
+    <col min="19" max="19" width="31.25" customWidth="1"/>
+    <col min="21" max="21" width="17.375" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1162,67 +1155,61 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
